--- a/public/demo-candidate-excel.xlsx
+++ b/public/demo-candidate-excel.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="demo-candidate" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>name</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>souvik.2sglobal@gmail.com</t>
+  </si>
+  <si>
+    <t>918974563210</t>
   </si>
 </sst>
 </file>
@@ -525,8 +528,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -874,7 +878,7 @@
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
     <col min="2" max="2" width="35.140625" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -884,7 +888,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -895,8 +899,8 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>1234567890</v>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -906,8 +910,8 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>9876543210</v>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -917,11 +921,15 @@
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
-        <v>5556667777</v>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="C2:C4" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>